--- a/elite-data/manifest-templates/EL_template_IndividualHumanTemplate.xlsx
+++ b/elite-data/manifest-templates/EL_template_IndividualHumanTemplate.xlsx
@@ -245,7 +245,7 @@
     <t>Ashkenazi Jewish</t>
   </si>
   <si>
-    <t>Not applicable</t>
+    <t>not applicable</t>
   </si>
   <si>
     <t>TRUE</t>
@@ -269,7 +269,7 @@
     <t>Asian</t>
   </si>
   <si>
-    <t>Not collected</t>
+    <t>not collected</t>
   </si>
   <si>
     <t>Alzheimer Disease</t>
@@ -323,7 +323,7 @@
     <t>anxiety</t>
   </si>
   <si>
-    <t>Unknown</t>
+    <t>unknown</t>
   </si>
   <si>
     <t>Autism Spectrum Disorder</t>
